--- a/docs/deliverables/out/Drop-1_Transactional/BRD-04_Collections/04_BIBS_TestPlan_BRD-04_Collections_v2.1.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/BRD-04_Collections/04_BIBS_TestPlan_BRD-04_Collections_v2.1.xlsx
@@ -34037,9 +34037,9 @@
       <c r="L275" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-CL-009: "Invoice &lt;invoice no&gt; is paid directly to the insurer / cancelled and has no premium to collect" (CLX_INVOICE_NOT_COLLECTIBLE)
-MSG-CL-010: "Invoice &lt;invoice no&gt; is not in the ledger" (CLX_INVOICE_UNKNOWN)
-MSG-CL-011: "&lt;editing by&gt; is editing &lt;invoice no&gt;" (CLX_ITEM_LOCKED)</t>
+MSG-CL-010: "Invoice &lt;invoice no&gt; is paid directly to the insurer / cancelled and has no premium to collect" (CLX_INVOICE_NOT_COLLECTIBLE)
+MSG-CL-011: "Invoice &lt;invoice no&gt; is not in the ledger" (CLX_INVOICE_UNKNOWN)
+MSG-CL-012: "&lt;editing by&gt; is editing &lt;invoice no&gt;" (CLX_ITEM_LOCKED)</t>
         </is>
       </c>
       <c r="M275" s="12" t="inlineStr">
@@ -34114,22 +34114,22 @@
       <c r="L276" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-CL-012: "A certificate tag needs the certificate number"
-MSG-CL-013: "Check pick-up"
-MSG-CL-014: "Choose a disposition"
-MSG-CL-015: "The pick-up date cannot be in the past"
-MSG-CL-016: "You are not allowed to update several accounts at once" (CLX_BULK_NOT_ALLOWED)
-MSG-CL-017: "The tagging category is A, B or C" (CLX_CATEGORY)
-MSG-CL-018: "Choose the 2307 path: certificate received or paid in cash" (CLX_CWT_PATH)
-MSG-CL-019: "'&lt;v&gt;' is not a date (yyyy-mm-dd)" (CLX_DISPOSITION_DETAIL)
-MSG-CL-020: "'&lt;v&gt;' is not an amount" (CLX_DISPOSITION_DETAIL)
-MSG-CL-021: "Give &lt;what&gt;" (CLX_DISPOSITION_DETAIL)
-MSG-CL-022: "This disposition is reserved to other roles" (CLX_DISPOSITION_NOT_ALLOWED)
-MSG-CL-023: "An effort cannot be in the future" (CLX_EFFORT_FUTURE)
-MSG-CL-024: "&lt;invoice no&gt; is &lt;status&gt;" (CLX_ITEM_CLOSED)
-MSG-CL-025: "&lt;invoice no&gt; belongs to another company" (CLX_ITEM_OTHER_COMPANY)
-MSG-CL-026: "Select at least one account" (CLX_NO_ACCOUNT)
-MSG-CL-027: "Select at most 500 accounts at once" (CLX_TOO_MANY_ACCOUNTS)</t>
+MSG-CL-013: "A certificate tag needs the certificate number"
+MSG-CL-014: "Check pick-up"
+MSG-CL-015: "Choose a disposition"
+MSG-CL-016: "The pick-up date cannot be in the past"
+MSG-CL-017: "You are not allowed to update several accounts at once" (CLX_BULK_NOT_ALLOWED)
+MSG-CL-018: "The tagging category is A, B or C" (CLX_CATEGORY)
+MSG-CL-019: "Choose the 2307 path: certificate received or paid in cash" (CLX_CWT_PATH)
+MSG-CL-020: "'&lt;v&gt;' is not a date (yyyy-mm-dd)" (CLX_DISPOSITION_DETAIL)
+MSG-CL-021: "'&lt;v&gt;' is not an amount" (CLX_DISPOSITION_DETAIL)
+MSG-CL-022: "Give &lt;what&gt;" (CLX_DISPOSITION_DETAIL)
+MSG-CL-023: "This disposition is reserved to other roles" (CLX_DISPOSITION_NOT_ALLOWED)
+MSG-CL-024: "An effort cannot be in the future" (CLX_EFFORT_FUTURE)
+MSG-CL-025: "&lt;invoice no&gt; is &lt;status&gt;" (CLX_ITEM_CLOSED)
+MSG-CL-026: "&lt;invoice no&gt; belongs to another company" (CLX_ITEM_OTHER_COMPANY)
+MSG-CL-027: "Select at least one account" (CLX_NO_ACCOUNT)
+MSG-CL-028: "Select at most 500 accounts at once" (CLX_TOO_MANY_ACCOUNTS)</t>
         </is>
       </c>
       <c r="M276" s="12" t="inlineStr">
@@ -34204,15 +34204,15 @@
       <c r="L277" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-CL-037: "Plan &lt;plan no&gt; has no billing cycle &lt;seq&gt;" (CLX_CYCLE_UNKNOWN)
-MSG-CL-038: "Billing frequency &lt;code&gt; has no cycle length defined" (CLX_FREQUENCY_UNSUPPORTED)
-MSG-CL-039: "A plan needs at least one installment" (CLX_PLAN_EMPTY)
-MSG-CL-040: "Enter at least one installment" (CLX_PLAN_EMPTY)
-MSG-CL-041: "Installment amounts must be positive and due dates increasing" (CLX_PLAN_ENTRY_INVALID)
-MSG-CL-042: "Plan &lt;plan no&gt; already schedules this account; cancel it first" (CLX_PLAN_EXISTS)
-MSG-CL-043: "Invoice &lt;invoice no&gt; has no outstanding premium to schedule" (CLX_PLAN_NOTHING_DUE)
-MSG-CL-044: "Plan &lt;plan no&gt; is &lt;status&gt; and cannot be cancelled" (CLX_PLAN_NOT_ACTIVE)
-MSG-CL-045: "Account &lt;arn&gt; has no booked policy year" (CLX_PLAN_NOT_BOOKED)</t>
+MSG-CL-038: "Plan &lt;plan no&gt; has no billing cycle &lt;seq&gt;" (CLX_CYCLE_UNKNOWN)
+MSG-CL-039: "Billing frequency &lt;code&gt; has no cycle length defined" (CLX_FREQUENCY_UNSUPPORTED)
+MSG-CL-040: "A plan needs at least one installment" (CLX_PLAN_EMPTY)
+MSG-CL-041: "Enter at least one installment" (CLX_PLAN_EMPTY)
+MSG-CL-042: "Installment amounts must be positive and due dates increasing" (CLX_PLAN_ENTRY_INVALID)
+MSG-CL-043: "Plan &lt;plan no&gt; already schedules this account; cancel it first" (CLX_PLAN_EXISTS)
+MSG-CL-044: "Invoice &lt;invoice no&gt; has no outstanding premium to schedule" (CLX_PLAN_NOTHING_DUE)
+MSG-CL-045: "Plan &lt;plan no&gt; is &lt;status&gt; and cannot be cancelled" (CLX_PLAN_NOT_ACTIVE)
+MSG-CL-046: "Account &lt;arn&gt; has no booked policy year" (CLX_PLAN_NOT_BOOKED)</t>
         </is>
       </c>
       <c r="M277" s="12" t="inlineStr">
@@ -34287,12 +34287,12 @@
       <c r="L278" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-CL-050: "The promised amount must be positive" (CLX_PROMISE_AMOUNT)
-MSG-CL-051: "The promise of &lt;invoice no&gt; is already &lt;status&gt;" (CLX_PROMISE_CLOSED)
-MSG-CL-052: "Enter the promised date; the day of the promise cannot be in the future" (CLX_PROMISE_DATES)
-MSG-CL-053: "The promised date cannot be before the day of the promise" (CLX_PROMISE_DATES)
-MSG-CL-054: "The installment does not bill invoice &lt;invoice no&gt;" (CLX_PROMISE_INSTALLMENT)
-MSG-CL-055: "Invoice &lt;invoice no&gt; has nothing to collect" (CLX_PROMISE_NOTHING_DUE)</t>
+MSG-CL-051: "The promised amount must be positive" (CLX_PROMISE_AMOUNT)
+MSG-CL-052: "The promise of &lt;invoice no&gt; is already &lt;status&gt;" (CLX_PROMISE_CLOSED)
+MSG-CL-053: "Enter the promised date; the day of the promise cannot be in the future" (CLX_PROMISE_DATES)
+MSG-CL-054: "The promised date cannot be before the day of the promise" (CLX_PROMISE_DATES)
+MSG-CL-055: "The installment does not bill invoice &lt;invoice no&gt;" (CLX_PROMISE_INSTALLMENT)
+MSG-CL-056: "Invoice &lt;invoice no&gt; has nothing to collect" (CLX_PROMISE_NOTHING_DUE)</t>
         </is>
       </c>
       <c r="M278" s="12" t="inlineStr">
@@ -34355,7 +34355,7 @@
       <c r="L279" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-CL-056: "Enter the &lt;label&gt;"</t>
+MSG-CL-057: "Enter the &lt;label&gt;"</t>
         </is>
       </c>
       <c r="M279" s="12" t="inlineStr">
@@ -34430,9 +34430,9 @@
       <c r="L280" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-CL-059: "Plan &lt;plan no&gt; is cancelled" (CLX_PLAN_NOT_ACTIVE)
-MSG-CL-060: "Cycle &lt;cycle seq&gt; of &lt;plan no&gt; is billed by &lt;soa no&gt;" (CLX_SOA_EXISTS)
-MSG-CL-061: "The period ends before it starts" (CLX_SOA_PERIOD)</t>
+MSG-CL-060: "Plan &lt;plan no&gt; is cancelled" (CLX_PLAN_NOT_ACTIVE)
+MSG-CL-061: "Cycle &lt;cycle seq&gt; of &lt;plan no&gt; is billed by &lt;soa no&gt;" (CLX_SOA_EXISTS)
+MSG-CL-062: "The period ends before it starts" (CLX_SOA_PERIOD)</t>
         </is>
       </c>
       <c r="M280" s="12" t="inlineStr">
@@ -34507,8 +34507,8 @@
       <c r="L281" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-CL-062: "Statement &lt;soa no&gt; is cancelled" (CLX_SOA_CANCELLED)
-MSG-CL-063: "Enter at least one recipient" (CLX_SOA_RECIPIENT)</t>
+MSG-CL-063: "Statement &lt;soa no&gt; is cancelled" (CLX_SOA_CANCELLED)
+MSG-CL-064: "Enter at least one recipient" (CLX_SOA_RECIPIENT)</t>
         </is>
       </c>
       <c r="M281" s="12" t="inlineStr">
@@ -34583,10 +34583,10 @@
       <c r="L282" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-CL-065: "'&lt;action&gt;' is not an escalation action" (CLX_ESCALATION_ACTION)
-MSG-CL-066: "&lt;username&gt; does not handle escalations" (CLX_ESCALATION_TARGET)
-MSG-CL-067: "Choose the level, and the user for a designated authority" (CLX_ESCALATION_TARGET)
-MSG-CL-068: "Describe how the escalation was resolved" (CLX_RESOLUTION_REQUIRED)</t>
+MSG-CL-066: "'&lt;action&gt;' is not an escalation action" (CLX_ESCALATION_ACTION)
+MSG-CL-067: "&lt;username&gt; does not handle escalations" (CLX_ESCALATION_TARGET)
+MSG-CL-068: "Choose the level, and the user for a designated authority" (CLX_ESCALATION_TARGET)
+MSG-CL-069: "Describe how the escalation was resolved" (CLX_RESOLUTION_REQUIRED)</t>
         </is>
       </c>
       <c r="M282" s="12" t="inlineStr">
@@ -34661,12 +34661,12 @@
       <c r="L283" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-CL-071: "The amount range ends below its start" (CLX_RULE_AMOUNTS)
-MSG-CL-072: "Enter the company and the rule code" (CLX_RULE_CODE)
-MSG-CL-073: "The rule cannot end before it becomes effective" (CLX_RULE_DATES)
-MSG-CL-074: "The threshold and the SLA hours must be positive" (CLX_RULE_INVALID)
-MSG-CL-075: "Name the user who receives the escalations of this rule" (CLX_RULE_TARGET)
-MSG-CL-076: "Escalation rule already exists: &lt;key&gt;" (DUPLICATE)</t>
+MSG-CL-072: "The amount range ends below its start" (CLX_RULE_AMOUNTS)
+MSG-CL-073: "Enter the company and the rule code" (CLX_RULE_CODE)
+MSG-CL-074: "The rule cannot end before it becomes effective" (CLX_RULE_DATES)
+MSG-CL-075: "The threshold and the SLA hours must be positive" (CLX_RULE_INVALID)
+MSG-CL-076: "Name the user who receives the escalations of this rule" (CLX_RULE_TARGET)
+MSG-CL-077: "Escalation rule already exists: &lt;key&gt;" (DUPLICATE)</t>
         </is>
       </c>
       <c r="M283" s="12" t="inlineStr">
@@ -34741,10 +34741,10 @@
       <c r="L284" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-CL-078: "Invoice number &lt;clean&gt; does not have the expected format (&lt;invoice pattern&gt;)" (CLX_INVOICE_FORMAT)
-MSG-CL-079: "Enter the invoice number to apply the payment to" (CLX_INVOICE_REQUIRED)
-MSG-CL-080: "Invoice &lt;clean&gt; is not in the invoice ledger" (CLX_INVOICE_UNKNOWN)
-MSG-CL-081: "&lt;unapplied ref&gt; has no unapplied balance left" (CLX_UNAPPLIED_NO_BALANCE)</t>
+MSG-CL-079: "Invoice number &lt;clean&gt; does not have the expected format (&lt;invoice pattern&gt;)" (CLX_INVOICE_FORMAT)
+MSG-CL-080: "Enter the invoice number to apply the payment to" (CLX_INVOICE_REQUIRED)
+MSG-CL-081: "Invoice &lt;clean&gt; is not in the invoice ledger" (CLX_INVOICE_UNKNOWN)
+MSG-CL-082: "&lt;unapplied ref&gt; has no unapplied balance left" (CLX_UNAPPLIED_NO_BALANCE)</t>
         </is>
       </c>
       <c r="M284" s="12" t="inlineStr">
@@ -34819,13 +34819,13 @@
       <c r="L285" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-CL-090: "&lt;handler&gt; is not an active collection handler" (CLX_HANDLER_NOT_ELIGIBLE)
-MSG-CL-091: "No account matches the selection" (CLX_REASSIGN_EMPTY)
-MSG-CL-092: "A temporary reassignment needs an end date after today" (CLX_REASSIGN_END_DATE)
-MSG-CL-093: "Choose a permanent or a temporary reassignment" (CLX_REASSIGN_KIND)
-MSG-CL-094: "Give the reason of the reassignment" (CLX_REASSIGN_REASON)
-MSG-CL-095: "Give the rule a name" (CLX_RULE_NAME)
-MSG-CL-096: "A range must start before it ends" (CLX_RULE_RANGE)</t>
+MSG-CL-091: "&lt;handler&gt; is not an active collection handler" (CLX_HANDLER_NOT_ELIGIBLE)
+MSG-CL-092: "No account matches the selection" (CLX_REASSIGN_EMPTY)
+MSG-CL-093: "A temporary reassignment needs an end date after today" (CLX_REASSIGN_END_DATE)
+MSG-CL-094: "Choose a permanent or a temporary reassignment" (CLX_REASSIGN_KIND)
+MSG-CL-095: "Give the reason of the reassignment" (CLX_REASSIGN_REASON)
+MSG-CL-096: "Give the rule a name" (CLX_RULE_NAME)
+MSG-CL-097: "A range must start before it ends" (CLX_RULE_RANGE)</t>
         </is>
       </c>
       <c r="M285" s="12" t="inlineStr">
@@ -34900,14 +34900,14 @@
       <c r="L286" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-CL-098: "The aging basis is BOOKING or INCEPTION" (CLX_AGING_BASIS)
-MSG-CL-099: "Aging bracket '&lt;text&gt;' ends before it starts" (CLX_AGING_BRACKETS_INVALID)
-MSG-CL-100: "Aging bracket '&lt;text&gt;' is not from-to or from+" (CLX_AGING_BRACKETS_INVALID)
-MSG-CL-101: "Aging brackets must be in ascending order: &lt;raw&gt;" (CLX_AGING_BRACKETS_INVALID)
-MSG-CL-102: "&lt;attribute&gt; is not an attribute of &lt;type code&gt;" (CLX_LOV_ATTRIBUTE_UNKNOWN)
-MSG-CL-103: "'&lt;value&gt;' is not a valid &lt;attribute&gt;" (CLX_LOV_ATTRIBUTE_VALUE)
-MSG-CL-104: "&lt;code&gt; is not a value of &lt;type code&gt;" (CLX_LOV_VALUE_UNKNOWN)
-MSG-CL-105: "&lt;key&gt; is not a Collections parameter" (CLX_PARAMETER_NOT_COLLECTIONS)</t>
+MSG-CL-099: "The aging basis is BOOKING or INCEPTION" (CLX_AGING_BASIS)
+MSG-CL-100: "Aging bracket '&lt;text&gt;' ends before it starts" (CLX_AGING_BRACKETS_INVALID)
+MSG-CL-101: "Aging bracket '&lt;text&gt;' is not from-to or from+" (CLX_AGING_BRACKETS_INVALID)
+MSG-CL-102: "Aging brackets must be in ascending order: &lt;raw&gt;" (CLX_AGING_BRACKETS_INVALID)
+MSG-CL-103: "&lt;attribute&gt; is not an attribute of &lt;type code&gt;" (CLX_LOV_ATTRIBUTE_UNKNOWN)
+MSG-CL-104: "'&lt;value&gt;' is not a valid &lt;attribute&gt;" (CLX_LOV_ATTRIBUTE_VALUE)
+MSG-CL-105: "&lt;code&gt; is not a value of &lt;type code&gt;" (CLX_LOV_VALUE_UNKNOWN)
+MSG-CL-106: "&lt;key&gt; is not a Collections parameter" (CLX_PARAMETER_NOT_COLLECTIONS)</t>
         </is>
       </c>
       <c r="M286" s="12" t="inlineStr">
@@ -34970,29 +34970,29 @@
       <c r="L287" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-CL-106: "Choose the billing frequency"
-MSG-CL-107: "Choose the disposition"
-MSG-CL-108: "Choose the escalation reason"
-MSG-CL-109: "Enter a positive amount, or leave it empty for the whole outstanding"
-MSG-CL-110: "Enter a positive threshold"
-MSG-CL-111: "Enter an amount above zero and at most &lt;balance&gt;"
-MSG-CL-112: "Enter at least one invoice number"
-MSG-CL-113: "Enter between 1 and 120 installments"
-MSG-CL-114: "Enter between 1 and 720 hours"
-MSG-CL-115: "Enter both dates"
-MSG-CL-116: "Enter the account reference number"
-MSG-CL-117: "Enter the first day"
-MSG-CL-118: "Enter the first due date"
-MSG-CL-119: "Enter the invoice number"
-MSG-CL-120: "Enter the invoice number to apply the payment to"
-MSG-CL-121: "Enter the promised payment date"
-MSG-CL-122: "Enter the rule code"
-MSG-CL-123: "Enter the rule name"
-MSG-CL-124: "Name the user who receives the escalations"
-MSG-CL-125: "The day of the promise cannot be in the future"
-MSG-CL-126: "The invoice number does not have the expected format"
-MSG-CL-127: "The promised date cannot be before the day of the promise"
-MSG-CL-128: "The rule cannot end before it starts"</t>
+MSG-CL-107: "Choose the billing frequency"
+MSG-CL-108: "Choose the disposition"
+MSG-CL-109: "Choose the escalation reason"
+MSG-CL-110: "Enter a positive amount, or leave it empty for the whole outstanding"
+MSG-CL-111: "Enter a positive threshold"
+MSG-CL-112: "Enter an amount above zero and at most &lt;balance&gt;"
+MSG-CL-113: "Enter at least one invoice number"
+MSG-CL-114: "Enter between 1 and 120 installments"
+MSG-CL-115: "Enter between 1 and 720 hours"
+MSG-CL-116: "Enter both dates"
+MSG-CL-117: "Enter the account reference number"
+MSG-CL-118: "Enter the first day"
+MSG-CL-119: "Enter the first due date"
+MSG-CL-120: "Enter the invoice number"
+MSG-CL-121: "Enter the invoice number to apply the payment to"
+MSG-CL-122: "Enter the promised payment date"
+MSG-CL-123: "Enter the rule code"
+MSG-CL-124: "Enter the rule name"
+MSG-CL-125: "Name the user who receives the escalations"
+MSG-CL-126: "The day of the promise cannot be in the future"
+MSG-CL-127: "The invoice number does not have the expected format"
+MSG-CL-128: "The promised date cannot be before the day of the promise"
+MSG-CL-129: "The rule cannot end before it starts"</t>
         </is>
       </c>
       <c r="M287" s="12" t="inlineStr">
@@ -35055,8 +35055,8 @@
       <c r="L288" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-CL-129: "&lt;Column&gt; '&lt;value&gt;' is not a valid &lt;number, date (yyyy-mm-dd), Y/N value&gt;"
-MSG-CL-130: "&lt;Column&gt; is mandatory"</t>
+MSG-CL-130: "&lt;Column&gt; '&lt;value&gt;' is not a valid &lt;number, date (yyyy-mm-dd), Y/N value&gt;"
+MSG-CL-131: "&lt;Column&gt; is mandatory"</t>
         </is>
       </c>
       <c r="M288" s="12" t="inlineStr">
@@ -35119,15 +35119,15 @@
       <c r="L289" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-CL-131: "&lt;target&gt; does not handle escalations"
-MSG-CL-132: "A promise amount needs the promise date"
-MSG-CL-133: "Escalation Level must be one of &lt;&gt;"
-MSG-CL-134: "Escalation Reason must be a code of the escalation reason list"
-MSG-CL-135: "Fill a promise, Escalate = Y or a worklist field"
-MSG-CL-136: "Invoice &lt;invoice&gt; has nothing to collect"
-MSG-CL-137: "Invoice &lt;invoice&gt; is not in the ledger"
-MSG-CL-138: "Name the user in Escalate To for a USER escalation"
-MSG-CL-139: "You are not allowed to escalate accounts"</t>
+MSG-CL-132: "&lt;target&gt; does not handle escalations"
+MSG-CL-133: "A promise amount needs the promise date"
+MSG-CL-134: "Escalation Level must be one of &lt;&gt;"
+MSG-CL-135: "Escalation Reason must be a code of the escalation reason list"
+MSG-CL-136: "Fill a promise, Escalate = Y or a worklist field"
+MSG-CL-137: "Invoice &lt;invoice&gt; has nothing to collect"
+MSG-CL-138: "Invoice &lt;invoice&gt; is not in the ledger"
+MSG-CL-139: "Name the user in Escalate To for a USER escalation"
+MSG-CL-140: "You are not allowed to escalate accounts"</t>
         </is>
       </c>
       <c r="M289" s="12" t="inlineStr">
@@ -35190,13 +35190,13 @@
       <c r="L290" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-CL-140: "You are not permitted to perform this action" (ACCESS_DENIED)
-MSG-CL-141: "The record was changed by another user. Please reload and try again." (CONCURRENT_MODIFICATION)
-MSG-CL-142: "The system could not complete the request. Try again; if it continues, contact support with the reference." (INTERNAL_ERROR)
-MSG-CL-143: "Parameter '&lt;name&gt;' has an invalid value" (MALFORMED_REQUEST)
-MSG-CL-144: "Required parameter '&lt;parameter name&gt;' is missing" (MALFORMED_REQUEST)
-MSG-CL-145: "The uploaded file is too large" (UPLOAD_TOO_LARGE)
-MSG-CL-146: "Invalid request" (VALIDATION_FAILED)</t>
+MSG-CL-141: "You are not permitted to perform this action" (ACCESS_DENIED)
+MSG-CL-142: "The record was changed by another user. Please reload and try again." (CONCURRENT_MODIFICATION)
+MSG-CL-143: "The system could not complete the request. Try again; if it continues, contact support with the reference." (INTERNAL_ERROR)
+MSG-CL-144: "Parameter '&lt;name&gt;' has an invalid value" (MALFORMED_REQUEST)
+MSG-CL-145: "Required parameter '&lt;parameter name&gt;' is missing" (MALFORMED_REQUEST)
+MSG-CL-146: "The uploaded file is too large" (UPLOAD_TOO_LARGE)
+MSG-CL-147: "Invalid request" (VALIDATION_FAILED)</t>
         </is>
       </c>
       <c r="M290" s="12" t="inlineStr">
